--- a/data/trans_dic/P41E_2023_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,16</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,92</t>
+          <t>0,5; 4,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,6</t>
+          <t>0,78; 4,85</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 18,52</t>
+          <t>8,86; 18,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 17,6</t>
+          <t>9,83; 17,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,28; 16,32</t>
+          <t>10,12; 16,37</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,3</t>
+          <t>0,55; 4,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,65</t>
+          <t>5,59; 11,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 6,75</t>
+          <t>3,46; 6,84</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,25</t>
+          <t>3,92; 12,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,07</t>
+          <t>0,44; 4,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,72</t>
+          <t>2,46; 7,13</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,58; 18,23</t>
+          <t>9,74; 18,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,4; 22,57</t>
+          <t>13,06; 22,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,13; 18,63</t>
+          <t>12,38; 18,55</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,08</t>
+          <t>0,75; 4,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,9</t>
+          <t>0,17; 2,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,54</t>
+          <t>0,5; 2,56</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,12; 32,53</t>
+          <t>6,29; 32,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,04; 39,7</t>
+          <t>31,5; 40,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,9; 34,11</t>
+          <t>9,78; 33,85</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,83; 11,89</t>
+          <t>6,33; 12,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,97</t>
+          <t>6,91; 13,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,08</t>
+          <t>7,58; 12,09</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes</t>
+          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1679</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3466</t>
+          <t>0; 3123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3527</t>
+          <t>0; 3565</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8703</t>
+          <t>0; 8707</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>577; 6621</t>
+          <t>557; 5533</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1389; 10510</t>
+          <t>1781; 11082</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15873; 34459</t>
+          <t>16485; 34786</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18671; 33863</t>
+          <t>18911; 33985</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38891; 61758</t>
+          <t>38301; 61943</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>888; 7281</t>
+          <t>926; 7134</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9409; 19843</t>
+          <t>9523; 19962</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12085; 22928</t>
+          <t>11758; 23239</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3207; 10586</t>
+          <t>3134; 10086</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>389; 3579</t>
+          <t>384; 3732</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4156; 12958</t>
+          <t>4133; 11974</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17677; 33657</t>
+          <t>17984; 33605</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19845; 33437</t>
+          <t>19352; 32975</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40375; 61994</t>
+          <t>41207; 61720</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1908; 11377</t>
+          <t>2083; 11276</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>855; 14413</t>
+          <t>847; 13092</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3764; 19720</t>
+          <t>3876; 19874</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>42007; 191976</t>
+          <t>37132; 190796</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>95078; 121589</t>
+          <t>96460; 123580</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>97749; 305828</t>
+          <t>87661; 303501</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>102485; 209182</t>
+          <t>111245; 214306</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>120512; 216301</t>
+          <t>115136; 216997</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>271699; 413790</t>
+          <t>259713; 414366</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Provincia-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,16</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 7,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,94</t>
+          <t>0,49; 4,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,85</t>
+          <t>0,61; 4,4</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 18,7</t>
+          <t>8,17; 17,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,83; 17,66</t>
+          <t>9,59; 17,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,12; 16,37</t>
+          <t>9,61; 15,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,21</t>
+          <t>0,6; 4,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 11,72</t>
+          <t>5,48; 11,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 6,84</t>
+          <t>3,42; 6,85</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,62</t>
+          <t>4,05; 13,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,24</t>
+          <t>0,41; 4,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 7,13</t>
+          <t>2,41; 7,38</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,74; 18,21</t>
+          <t>10,3; 18,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,06; 22,26</t>
+          <t>12,76; 22,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,38; 18,55</t>
+          <t>12,45; 18,29</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,04</t>
+          <t>0,57; 3,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 2,64</t>
+          <t>0,77; 3,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,56</t>
+          <t>0,92; 2,97</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,29; 32,33</t>
+          <t>26,04; 34,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,5; 40,35</t>
+          <t>31,12; 39,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,78; 33,85</t>
+          <t>29,23; 35,54</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,19</t>
+          <t>9,85; 12,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,01</t>
+          <t>11,11; 13,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,09</t>
+          <t>10,88; 12,76</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>984</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>0; 3138</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3565</t>
+          <t>0; 3891</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2597</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4670</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8707</t>
+          <t>0; 8566</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>557; 5533</t>
+          <t>582; 5687</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1781; 11082</t>
+          <t>1464; 10537</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>23228</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50026</t>
+          <t>48589</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16485; 34786</t>
+          <t>15421; 33263</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18911; 33985</t>
+          <t>18919; 34282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38301; 61943</t>
+          <t>37115; 60814</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>15161</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>18461</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>926; 7134</t>
+          <t>1180; 8290</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9523; 19962</t>
+          <t>10358; 21478</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11758; 23239</t>
+          <t>13152; 26332</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>8038</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3134; 10086</t>
+          <t>3554; 11755</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>384; 3732</t>
+          <t>393; 4589</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4133; 11974</t>
+          <t>4438; 13584</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>25011</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25548</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>50558</t>
+          <t>51400</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>17984; 33605</t>
+          <t>19167; 34047</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19352; 32975</t>
+          <t>19281; 34232</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41207; 61720</t>
+          <t>41959; 61666</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11277</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2083; 11276</t>
+          <t>1866; 11432</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>847; 13092</t>
+          <t>2695; 13467</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3876; 19874</t>
+          <t>6191; 20059</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>119645</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>108392</t>
+          <t>124000</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>216263</t>
+          <t>243645</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>37132; 190796</t>
+          <t>103221; 136732</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>96460; 123580</t>
+          <t>109886; 139609</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>87661; 303501</t>
+          <t>219086; 266333</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>174371</t>
+          <t>186425</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>183107</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>357478</t>
+          <t>387064</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>111245; 214306</t>
+          <t>163464; 210543</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>115136; 216997</t>
+          <t>179746; 222327</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>259713; 414366</t>
+          <t>356631; 418249</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P41E_2023_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P41E_2023_R-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
+          <t>Población que con respecto al último año sus relaciones sexuales no han sido satisfactorias para ambas partes (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
